--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -205,6 +205,9 @@
   </si>
   <si>
     <t>bit confused</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -1726,26 +1729,50 @@
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="18"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="18">
+        <v>46266</v>
+      </c>
+      <c r="B8" s="19">
+        <v>472</v>
+      </c>
+      <c r="C8" s="19">
+        <v>10</v>
+      </c>
+      <c r="D8" s="19">
+        <v>60</v>
+      </c>
+      <c r="E8" s="19">
+        <v>40</v>
+      </c>
+      <c r="F8" s="19">
+        <v>250</v>
+      </c>
+      <c r="G8" s="19">
+        <v>6</v>
+      </c>
+      <c r="H8" s="19">
+        <v>15</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>847</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="20"/>
-      <c r="N8" s="21"/>
+        <v>593</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="21" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1775,26 +1775,48 @@
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="18"/>
+      <c r="A9" s="18">
+        <v>46267</v>
+      </c>
       <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="15" t="str">
+      <c r="C9" s="19">
+        <v>12</v>
+      </c>
+      <c r="D9" s="19">
+        <v>30</v>
+      </c>
+      <c r="E9" s="19">
+        <v>20</v>
+      </c>
+      <c r="F9" s="19">
+        <v>300</v>
+      </c>
+      <c r="G9" s="19">
+        <v>6</v>
+      </c>
+      <c r="H9" s="19">
+        <v>25</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>387</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="21"/>
+        <v>1053</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N9" s="21" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -208,6 +208,12 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>bit elated</t>
   </si>
 </sst>
 </file>
@@ -1819,26 +1825,50 @@
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="18"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="18">
+        <v>46268</v>
+      </c>
+      <c r="B10" s="19">
+        <v>440</v>
+      </c>
+      <c r="C10" s="19">
+        <v>15</v>
+      </c>
+      <c r="D10" s="19">
+        <v>45</v>
+      </c>
+      <c r="E10" s="19">
+        <v>10</v>
+      </c>
+      <c r="F10" s="19">
+        <v>280</v>
+      </c>
+      <c r="G10" s="19">
+        <v>5</v>
+      </c>
+      <c r="H10" s="19">
+        <v>15</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>805</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="21"/>
+        <v>635</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N10" s="21" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -214,6 +214,9 @@
   </si>
   <si>
     <t>bit elated</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
 </sst>
 </file>
@@ -1871,26 +1874,48 @@
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="18"/>
+      <c r="A11" s="18">
+        <v>46269</v>
+      </c>
       <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="15" t="str">
+      <c r="C11" s="19">
+        <v>12</v>
+      </c>
+      <c r="D11" s="19">
+        <v>30</v>
+      </c>
+      <c r="E11" s="19">
+        <v>20</v>
+      </c>
+      <c r="F11" s="19">
+        <v>200</v>
+      </c>
+      <c r="G11" s="19">
+        <v>4</v>
+      </c>
+      <c r="H11" s="19">
+        <v>120</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>382</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="20"/>
-      <c r="L11" s="20"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="21"/>
+        <v>1058</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M11" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N11" s="21" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -217,6 +217,9 @@
   </si>
   <si>
     <t>High</t>
+  </si>
+  <si>
+    <t>need to improve focus</t>
   </si>
 </sst>
 </file>
@@ -1918,26 +1921,48 @@
       </c>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="18"/>
+      <c r="A12" s="18">
+        <v>46270</v>
+      </c>
       <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="15" t="str">
+      <c r="C12" s="19">
+        <v>20</v>
+      </c>
+      <c r="D12" s="19">
+        <v>120</v>
+      </c>
+      <c r="E12" s="19">
+        <v>15</v>
+      </c>
+      <c r="F12" s="19">
+        <v>0</v>
+      </c>
+      <c r="G12" s="19">
+        <v>0</v>
+      </c>
+      <c r="H12" s="19">
+        <v>80</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>235</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
-      <c r="M12" s="20"/>
-      <c r="N12" s="21"/>
+        <v>1205</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M12" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N12" s="21" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -220,6 +220,9 @@
   </si>
   <si>
     <t>need to improve focus</t>
+  </si>
+  <si>
+    <t>all good</t>
   </si>
 </sst>
 </file>
@@ -1965,26 +1968,50 @@
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="18"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="18">
+        <v>46271</v>
+      </c>
+      <c r="B13" s="19">
+        <v>460</v>
+      </c>
+      <c r="C13" s="19">
+        <v>20</v>
+      </c>
+      <c r="D13" s="19">
+        <v>110</v>
+      </c>
+      <c r="E13" s="19">
+        <v>30</v>
+      </c>
+      <c r="F13" s="19">
+        <v>0</v>
+      </c>
+      <c r="G13" s="19">
+        <v>0</v>
+      </c>
+      <c r="H13" s="19">
+        <v>240</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="20"/>
-      <c r="L13" s="20"/>
-      <c r="M13" s="20"/>
-      <c r="N13" s="21"/>
+        <v>580</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N13" s="21" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -223,6 +223,12 @@
   </si>
   <si>
     <t>all good</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>demotivated</t>
   </si>
 </sst>
 </file>
@@ -2014,26 +2020,50 @@
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="18"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="18">
+        <v>46272</v>
+      </c>
+      <c r="B14" s="19">
+        <v>450</v>
+      </c>
+      <c r="C14" s="19">
+        <v>10</v>
+      </c>
+      <c r="D14" s="19">
+        <v>40</v>
+      </c>
+      <c r="E14" s="19">
+        <v>50</v>
+      </c>
+      <c r="F14" s="19">
+        <v>250</v>
+      </c>
+      <c r="G14" s="19">
+        <v>5</v>
+      </c>
+      <c r="H14" s="19">
+        <v>240</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
-      <c r="M14" s="20"/>
-      <c r="N14" s="21"/>
+        <v>400</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="M14" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N14" s="21" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -229,6 +229,9 @@
   </si>
   <si>
     <t>demotivated</t>
+  </si>
+  <si>
+    <t>tired</t>
   </si>
 </sst>
 </file>
@@ -2066,26 +2069,50 @@
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="18"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="18">
+        <v>46273</v>
+      </c>
+      <c r="B15" s="19">
+        <v>470</v>
+      </c>
+      <c r="C15" s="19">
+        <v>12</v>
+      </c>
+      <c r="D15" s="19">
+        <v>30</v>
+      </c>
+      <c r="E15" s="19">
+        <v>50</v>
+      </c>
+      <c r="F15" s="19">
+        <v>250</v>
+      </c>
+      <c r="G15" s="19">
+        <v>6</v>
+      </c>
+      <c r="H15" s="19">
+        <v>160</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>972</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="21"/>
+        <v>468</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N15" s="21" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2115,26 +2115,50 @@
       </c>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="18">
+        <v>46274</v>
+      </c>
+      <c r="B16" s="19">
+        <v>460</v>
+      </c>
+      <c r="C16" s="19">
+        <v>30</v>
+      </c>
+      <c r="D16" s="19">
+        <v>60</v>
+      </c>
+      <c r="E16" s="19">
+        <v>56</v>
+      </c>
+      <c r="F16" s="19">
+        <v>250</v>
+      </c>
+      <c r="G16" s="19">
+        <v>5</v>
+      </c>
+      <c r="H16" s="19">
+        <v>200</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1056</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="21"/>
+        <v>384</v>
+      </c>
+      <c r="K16" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M16" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N16" s="21" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,6 +232,9 @@
   </si>
   <si>
     <t>tired</t>
+  </si>
+  <si>
+    <t>doubting mysekf</t>
   </si>
 </sst>
 </file>
@@ -2161,26 +2164,50 @@
       </c>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="18"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="18">
+        <v>46275</v>
+      </c>
+      <c r="B17" s="19">
+        <v>470</v>
+      </c>
+      <c r="C17" s="19">
+        <v>20</v>
+      </c>
+      <c r="D17" s="19">
+        <v>60</v>
+      </c>
+      <c r="E17" s="19">
+        <v>15</v>
+      </c>
+      <c r="F17" s="19">
+        <v>0</v>
+      </c>
+      <c r="G17" s="19">
+        <v>0</v>
+      </c>
+      <c r="H17" s="19">
+        <v>400</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>965</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="20"/>
-      <c r="N17" s="21"/>
+        <v>475</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M17" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N17" s="21" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -235,6 +235,9 @@
   </si>
   <si>
     <t>doubting mysekf</t>
+  </si>
+  <si>
+    <t>bit sad</t>
   </si>
 </sst>
 </file>
@@ -2210,26 +2213,50 @@
       </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="18"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="18">
+        <v>46276</v>
+      </c>
+      <c r="B18" s="19">
+        <v>480</v>
+      </c>
+      <c r="C18" s="19">
+        <v>45</v>
+      </c>
+      <c r="D18" s="19">
+        <v>56</v>
+      </c>
+      <c r="E18" s="19">
+        <v>35</v>
+      </c>
+      <c r="F18" s="19">
+        <v>200</v>
+      </c>
+      <c r="G18" s="19">
+        <v>4</v>
+      </c>
+      <c r="H18" s="19">
+        <v>300</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1116</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-      <c r="M18" s="20"/>
-      <c r="N18" s="21"/>
+        <v>324</v>
+      </c>
+      <c r="K18" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M18" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N18" s="21" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="18"/>

--- a/12628474.xlsx
+++ b/12628474.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2259,26 +2259,48 @@
       </c>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="18"/>
+      <c r="A19" s="18">
+        <v>46277</v>
+      </c>
       <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="15" t="str">
+      <c r="C19" s="19">
+        <v>20</v>
+      </c>
+      <c r="D19" s="19">
+        <v>120</v>
+      </c>
+      <c r="E19" s="19">
+        <v>30</v>
+      </c>
+      <c r="F19" s="19">
+        <v>0</v>
+      </c>
+      <c r="G19" s="19">
+        <v>0</v>
+      </c>
+      <c r="H19" s="19">
+        <v>400</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>570</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="20"/>
-      <c r="N19" s="21"/>
+        <v>870</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="M19" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N19" s="21" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="18"/>
